--- a/26-tdy/02-26-sny.xlsx
+++ b/26-tdy/02-26-sny.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\tdy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\26-tdy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58411BE3-11A9-44D0-8312-F0B711D9CB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343588F4-9310-4FE6-A551-F5F77414C552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="773" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="524">
   <si>
     <t>Ödeme Teminat Tablosu</t>
   </si>
@@ -1677,13 +1677,13 @@
     <t>30-09-2025 – 31-09-2026</t>
   </si>
   <si>
-    <t>sny C</t>
-  </si>
-  <si>
     <t xml:space="preserve">arsa önüne malzeme yığıntısı var </t>
   </si>
   <si>
     <t>2025 - 12 ay</t>
+  </si>
+  <si>
+    <t>sny CD Ali demirel</t>
   </si>
 </sst>
 </file>
@@ -2781,7 +2781,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="354">
+  <cellXfs count="356">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3372,6 +3372,8 @@
     <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="22" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="24">
     <cellStyle name="Accent" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3413,8 +3415,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8CD5396B-AF3B-4E02-B816-7FFFC3CDB203}" name="Tablo142" displayName="Tablo142" ref="A25:J42" totalsRowShown="0">
-  <autoFilter ref="A25:J42" xr:uid="{2302621F-B3C3-4429-8379-CD484CA39087}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8CD5396B-AF3B-4E02-B816-7FFFC3CDB203}" name="Tablo142" displayName="Tablo142" ref="A30:J47" totalsRowShown="0">
+  <autoFilter ref="A30:J47" xr:uid="{2302621F-B3C3-4429-8379-CD484CA39087}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{411BB1D6-998E-4B35-80A9-FDD140F71C9B}" name="Tarih"/>
     <tableColumn id="2" xr3:uid="{279E89D5-CF7B-4AA4-8F3F-A2F7799804F3}" name="Açıklama"/>
@@ -6543,7 +6545,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F3B4BF-5428-4CFE-9CCD-7224C312B45E}">
-  <dimension ref="A2:J76"/>
+  <dimension ref="A2:J81"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -6624,7 +6626,7 @@
         <v>449</v>
       </c>
       <c r="H7" s="122">
-        <f>H26*-1</f>
+        <f>H31*-1</f>
         <v>139111.94400000002</v>
       </c>
     </row>
@@ -6648,7 +6650,7 @@
       <c r="F9" s="340"/>
       <c r="G9" s="125"/>
       <c r="H9" s="126">
-        <f t="shared" ref="H9:H21" si="0">H8-E9</f>
+        <f t="shared" ref="H9:H22" si="0">H8-E9</f>
         <v>277861.70400000003</v>
       </c>
     </row>
@@ -6873,290 +6875,219 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="123">
+      <c r="A21" s="354">
         <v>46034</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>517</v>
       </c>
       <c r="C21" s="94"/>
-      <c r="D21" s="90"/>
+      <c r="D21" s="355"/>
       <c r="E21" s="124">
         <v>25000</v>
       </c>
-      <c r="H21" s="90">
+      <c r="F21" s="338"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="355">
         <f t="shared" si="0"/>
         <v>62861.704000000027</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="123"/>
+      <c r="A22" s="354">
+        <v>46058</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>517</v>
+      </c>
       <c r="C22" s="94"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="124"/>
-      <c r="H22" s="90"/>
+      <c r="D22" s="355"/>
+      <c r="E22" s="124">
+        <v>25000</v>
+      </c>
+      <c r="F22" s="338"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="355">
+        <f t="shared" si="0"/>
+        <v>37861.704000000027</v>
+      </c>
     </row>
     <row r="23" spans="1:10">
+      <c r="A23" s="123"/>
       <c r="C23" s="94"/>
       <c r="D23" s="90"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="95"/>
-    </row>
-    <row r="24" spans="1:10" ht="15.75">
-      <c r="B24" s="96" t="s">
+      <c r="E23" s="124"/>
+      <c r="H23" s="90"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="123"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="124"/>
+      <c r="H24" s="90"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="123"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="124"/>
+      <c r="H25" s="90"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="123"/>
+      <c r="C26" s="94"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="124"/>
+      <c r="H26" s="90"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="123"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="124"/>
+      <c r="H27" s="90"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="C28" s="94"/>
+      <c r="D28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="95"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75">
+      <c r="B29" s="96" t="s">
         <v>284</v>
       </c>
-      <c r="D24" s="251">
+      <c r="D29" s="251">
         <v>0.76461599999999996</v>
       </c>
-      <c r="E24" s="251">
-        <f>1-D24</f>
+      <c r="E29" s="251">
+        <f>1-D29</f>
         <v>0.23538400000000004</v>
       </c>
-      <c r="H24" s="95"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="116" t="s">
+      <c r="H29" s="95"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="116" t="s">
+      <c r="B30" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="127" t="s">
+      <c r="C30" s="127" t="s">
         <v>285</v>
       </c>
-      <c r="D25" s="128" t="s">
+      <c r="D30" s="128" t="s">
         <v>286</v>
       </c>
-      <c r="E25" s="127" t="s">
+      <c r="E30" s="127" t="s">
         <v>287</v>
       </c>
-      <c r="F25" s="341" t="s">
+      <c r="F30" s="341" t="s">
         <v>288</v>
       </c>
-      <c r="G25" s="127" t="s">
+      <c r="G30" s="127" t="s">
         <v>289</v>
       </c>
-      <c r="H25" s="130" t="s">
+      <c r="H30" s="130" t="s">
         <v>245</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I30" t="s">
         <v>484</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J30" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="116"/>
-      <c r="B26" s="117" t="s">
+    <row r="31" spans="1:10">
+      <c r="A31" s="116"/>
+      <c r="B31" s="117" t="s">
         <v>292</v>
       </c>
-      <c r="C26" s="118">
-        <f>SUBTOTAL(109,C27:C41)</f>
+      <c r="C31" s="118">
+        <f>SUBTOTAL(109,C32:C46)</f>
         <v>591000</v>
       </c>
-      <c r="D26" s="118">
-        <f>SUBTOTAL(109,D27:D41)</f>
+      <c r="D31" s="118">
+        <f>SUBTOTAL(109,D32:D46)</f>
         <v>591000</v>
       </c>
-      <c r="E26" s="118">
-        <f>SUM(E27:E41)</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="342"/>
-      <c r="G26" s="118">
-        <f>SUBTOTAL(109,$G$27:$G$41)</f>
+      <c r="E31" s="118">
+        <f>SUM(E32:E46)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="342"/>
+      <c r="G31" s="118">
+        <f>SUBTOTAL(109,$G$32:$G$46)</f>
         <v>-139111.94400000002</v>
       </c>
-      <c r="H26" s="118">
-        <f>H27</f>
+      <c r="H31" s="118">
+        <f>H32</f>
         <v>-139111.94400000002</v>
       </c>
-      <c r="J26" s="98"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="99">
+      <c r="J31" s="98"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="99">
         <v>46021</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B32" t="s">
         <v>290</v>
       </c>
-      <c r="D27" s="100">
-        <f t="shared" ref="D27:D40" si="2">IF(F27=1,$C27,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="101">
-        <f t="shared" ref="E27:E41" si="3">IF(F27=0,C27*$E$24*-1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="343">
-        <v>0</v>
-      </c>
-      <c r="G27" s="100">
-        <f t="shared" ref="G27:G40" si="4">IF(F27=1,C27*$E$24*-1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="95">
-        <f t="shared" ref="H27:H40" si="5">H28+G27</f>
+      <c r="D32" s="100">
+        <f t="shared" ref="D32:D45" si="2">IF(F32=1,$C32,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="101">
+        <f t="shared" ref="E32:E46" si="3">IF(F32=0,C32*$E$29*-1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="343">
+        <v>0</v>
+      </c>
+      <c r="G32" s="100">
+        <f t="shared" ref="G32:G45" si="4">IF(F32=1,C32*$E$29*-1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="95">
+        <f t="shared" ref="H32:H45" si="5">H33+G32</f>
         <v>-139111.94400000002</v>
       </c>
-      <c r="J27" s="98"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="227">
+      <c r="J32" s="98"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="227">
         <v>45992</v>
       </c>
-      <c r="B28" s="228" t="s">
-        <v>521</v>
-      </c>
-      <c r="C28" s="233">
+      <c r="B33" s="228" t="s">
+        <v>523</v>
+      </c>
+      <c r="C33" s="233">
         <v>301000</v>
       </c>
-      <c r="D28" s="100">
+      <c r="D33" s="100">
         <f t="shared" si="2"/>
         <v>301000</v>
       </c>
-      <c r="E28" s="101">
+      <c r="E33" s="101">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F28" s="343">
+      <c r="F33" s="343">
         <v>1</v>
       </c>
-      <c r="G28" s="100">
+      <c r="G33" s="100">
         <f t="shared" si="4"/>
         <v>-70850.584000000017</v>
       </c>
-      <c r="H28" s="95">
+      <c r="H33" s="95">
         <f t="shared" si="5"/>
         <v>-139111.94400000002</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="229"/>
-      <c r="B29" s="230"/>
-      <c r="C29" s="234"/>
-      <c r="D29" s="100">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="101">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="343">
-        <v>0</v>
-      </c>
-      <c r="G29" s="100">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="95">
-        <f t="shared" si="5"/>
-        <v>-68261.360000000015</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="229"/>
-      <c r="B30" s="230"/>
-      <c r="C30" s="234"/>
-      <c r="D30" s="100">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="101">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="343">
-        <v>0</v>
-      </c>
-      <c r="G30" s="100">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="95">
-        <f t="shared" si="5"/>
-        <v>-68261.360000000015</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="227"/>
-      <c r="B31" s="231"/>
-      <c r="C31" s="233"/>
-      <c r="D31" s="100">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="101">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="343">
-        <v>0</v>
-      </c>
-      <c r="G31" s="100">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="95">
-        <f t="shared" si="5"/>
-        <v>-68261.360000000015</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="227"/>
-      <c r="B32" s="232"/>
-      <c r="C32" s="235"/>
-      <c r="D32" s="100">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E32" s="101">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="343">
-        <v>0</v>
-      </c>
-      <c r="G32" s="100">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="95">
-        <f t="shared" si="5"/>
-        <v>-68261.360000000015</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="227"/>
-      <c r="B33" s="228"/>
-      <c r="C33" s="233"/>
-      <c r="D33" s="100">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="101">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="343">
-        <v>0</v>
-      </c>
-      <c r="G33" s="100">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="95">
-        <f t="shared" si="5"/>
-        <v>-68261.360000000015</v>
-      </c>
-    </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="227"/>
-      <c r="B34" s="228"/>
-      <c r="C34" s="233"/>
+      <c r="A34" s="229"/>
+      <c r="B34" s="230"/>
+      <c r="C34" s="234"/>
       <c r="D34" s="100">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -7178,9 +7109,9 @@
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="227"/>
-      <c r="B35" s="228"/>
-      <c r="C35" s="233"/>
+      <c r="A35" s="229"/>
+      <c r="B35" s="230"/>
+      <c r="C35" s="234"/>
       <c r="D35" s="100">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -7202,9 +7133,9 @@
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="229"/>
+      <c r="A36" s="227"/>
       <c r="B36" s="231"/>
-      <c r="C36" s="234"/>
+      <c r="C36" s="233"/>
       <c r="D36" s="100">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -7226,9 +7157,9 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="225"/>
-      <c r="B37" s="226"/>
-      <c r="C37" s="236"/>
+      <c r="A37" s="227"/>
+      <c r="B37" s="232"/>
+      <c r="C37" s="235"/>
       <c r="D37" s="100">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -7250,9 +7181,9 @@
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="229"/>
-      <c r="B38" s="231"/>
-      <c r="C38" s="237"/>
+      <c r="A38" s="227"/>
+      <c r="B38" s="228"/>
+      <c r="C38" s="233"/>
       <c r="D38" s="100">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -7274,9 +7205,9 @@
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="229"/>
-      <c r="B39" s="230"/>
-      <c r="C39" s="234"/>
+      <c r="A39" s="227"/>
+      <c r="B39" s="228"/>
+      <c r="C39" s="233"/>
       <c r="D39" s="100">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -7299,7 +7230,7 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="227"/>
-      <c r="B40" s="230"/>
+      <c r="B40" s="228"/>
       <c r="C40" s="233"/>
       <c r="D40" s="100">
         <f t="shared" si="2"/>
@@ -7310,7 +7241,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="343">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="100">
         <f t="shared" si="4"/>
@@ -7320,428 +7251,548 @@
         <f t="shared" si="5"/>
         <v>-68261.360000000015</v>
       </c>
-      <c r="J40">
-        <v>5</v>
-      </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="174">
-        <v>45660</v>
-      </c>
-      <c r="B41" s="175" t="s">
-        <v>451</v>
-      </c>
-      <c r="C41" s="176">
-        <v>290000</v>
-      </c>
+      <c r="A41" s="229"/>
+      <c r="B41" s="231"/>
+      <c r="C41" s="234"/>
       <c r="D41" s="100">
-        <f>IF(F41=1,$C41,0)</f>
-        <v>290000</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="E41" s="101">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F41" s="344">
+      <c r="F41" s="343">
+        <v>0</v>
+      </c>
+      <c r="G41" s="100">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="95">
+        <f t="shared" si="5"/>
+        <v>-68261.360000000015</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="225"/>
+      <c r="B42" s="226"/>
+      <c r="C42" s="236"/>
+      <c r="D42" s="100">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E42" s="101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="343">
+        <v>0</v>
+      </c>
+      <c r="G42" s="100">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="95">
+        <f t="shared" si="5"/>
+        <v>-68261.360000000015</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="229"/>
+      <c r="B43" s="231"/>
+      <c r="C43" s="237"/>
+      <c r="D43" s="100">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E43" s="101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="343">
+        <v>0</v>
+      </c>
+      <c r="G43" s="100">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="95">
+        <f t="shared" si="5"/>
+        <v>-68261.360000000015</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="229"/>
+      <c r="B44" s="230"/>
+      <c r="C44" s="234"/>
+      <c r="D44" s="100">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E44" s="101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="343">
+        <v>0</v>
+      </c>
+      <c r="G44" s="100">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="95">
+        <f t="shared" si="5"/>
+        <v>-68261.360000000015</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="227"/>
+      <c r="B45" s="230"/>
+      <c r="C45" s="233"/>
+      <c r="D45" s="100">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E45" s="101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="343">
         <v>1</v>
       </c>
-      <c r="G41" s="100">
-        <f>IF(F41=1,C41*$E$24*-1,0)</f>
+      <c r="G45" s="100">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="95">
+        <f t="shared" si="5"/>
         <v>-68261.360000000015</v>
       </c>
-      <c r="H41" s="95">
-        <f>G41</f>
+      <c r="J45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="174">
+        <v>45660</v>
+      </c>
+      <c r="B46" s="175" t="s">
+        <v>451</v>
+      </c>
+      <c r="C46" s="176">
+        <v>290000</v>
+      </c>
+      <c r="D46" s="100">
+        <f>IF(F46=1,$C46,0)</f>
+        <v>290000</v>
+      </c>
+      <c r="E46" s="101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="344">
+        <v>1</v>
+      </c>
+      <c r="G46" s="100">
+        <f>IF(F46=1,C46*$E$29*-1,0)</f>
         <v>-68261.360000000015</v>
       </c>
-      <c r="J41">
+      <c r="H46" s="95">
+        <f>G46</f>
+        <v>-68261.360000000015</v>
+      </c>
+      <c r="J46">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
-      <c r="J42" t="s">
+    <row r="47" spans="1:10">
+      <c r="J47" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
-      <c r="C43" s="95"/>
-      <c r="D43" s="95"/>
-      <c r="E43" s="95"/>
-      <c r="G43" s="95"/>
-      <c r="H43" s="95"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="C44" s="100" t="s">
-        <v>249</v>
-      </c>
-      <c r="D44" s="95" t="s">
-        <v>293</v>
-      </c>
-      <c r="E44" s="95" t="s">
-        <v>294</v>
-      </c>
-      <c r="G44" s="106"/>
-      <c r="H44" s="106"/>
-      <c r="I44" s="107"/>
-    </row>
-    <row r="45" spans="1:10" ht="15.75">
-      <c r="B45" t="s">
-        <v>247</v>
-      </c>
-      <c r="C45" s="108">
-        <v>1</v>
-      </c>
-      <c r="D45" s="252">
-        <f>D24</f>
-        <v>0.76461599999999996</v>
-      </c>
-      <c r="E45" s="252">
-        <f>1-D45</f>
-        <v>0.23538400000000004</v>
-      </c>
-      <c r="H45" s="95"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="B46" t="s">
-        <v>295</v>
-      </c>
-      <c r="C46" s="109">
-        <f>$D$26*C45</f>
-        <v>591000</v>
-      </c>
-      <c r="D46" s="110">
-        <f>$D$26*D45</f>
-        <v>451888.05599999998</v>
-      </c>
-      <c r="E46" s="110">
-        <f>$D$26*E45</f>
-        <v>139111.94400000002</v>
-      </c>
-      <c r="G46" s="345"/>
-      <c r="H46" s="346"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="B47" t="s">
-        <v>248</v>
-      </c>
-      <c r="C47" s="100">
-        <f>D47+E47</f>
-        <v>591000</v>
-      </c>
-      <c r="D47" s="95">
-        <f>C46-E47</f>
-        <v>451888.05599999998</v>
-      </c>
-      <c r="E47" s="95">
-        <f>$H$26*-1</f>
-        <v>139111.94400000002</v>
-      </c>
-      <c r="G47" s="337"/>
-      <c r="H47" s="95"/>
-      <c r="J47" s="95"/>
-    </row>
     <row r="48" spans="1:10">
-      <c r="B48" t="s">
-        <v>296</v>
-      </c>
-      <c r="C48" s="100">
-        <f>C46-C47</f>
-        <v>0</v>
-      </c>
-      <c r="D48" s="95">
-        <f>D46-D47</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="95">
-        <f>E46-E47</f>
-        <v>0</v>
-      </c>
+      <c r="C48" s="95"/>
+      <c r="D48" s="95"/>
+      <c r="E48" s="95"/>
       <c r="G48" s="95"/>
       <c r="H48" s="95"/>
-      <c r="J48" s="95"/>
-    </row>
-    <row r="49" spans="2:10" ht="13.5" thickBot="1">
-      <c r="C49" s="112"/>
-      <c r="D49" s="112"/>
-      <c r="E49" s="112"/>
-      <c r="J49" s="95"/>
-    </row>
-    <row r="50" spans="2:10">
-      <c r="J50" s="95"/>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="C49" s="100" t="s">
+        <v>249</v>
+      </c>
+      <c r="D49" s="95" t="s">
+        <v>293</v>
+      </c>
+      <c r="E49" s="95" t="s">
+        <v>294</v>
+      </c>
+      <c r="G49" s="106"/>
+      <c r="H49" s="106"/>
+      <c r="I49" s="107"/>
+    </row>
+    <row r="50" spans="2:10" ht="15.75">
+      <c r="B50" t="s">
+        <v>247</v>
+      </c>
+      <c r="C50" s="108">
+        <v>1</v>
+      </c>
+      <c r="D50" s="252">
+        <f>D29</f>
+        <v>0.76461599999999996</v>
+      </c>
+      <c r="E50" s="252">
+        <f>1-D50</f>
+        <v>0.23538400000000004</v>
+      </c>
+      <c r="H50" s="95"/>
     </row>
     <row r="51" spans="2:10">
-      <c r="C51" s="5" t="s">
+      <c r="B51" t="s">
+        <v>295</v>
+      </c>
+      <c r="C51" s="109">
+        <f>$D$31*C50</f>
+        <v>591000</v>
+      </c>
+      <c r="D51" s="110">
+        <f>$D$31*D50</f>
+        <v>451888.05599999998</v>
+      </c>
+      <c r="E51" s="110">
+        <f>$D$31*E50</f>
+        <v>139111.94400000002</v>
+      </c>
+      <c r="G51" s="345"/>
+      <c r="H51" s="346"/>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" t="s">
+        <v>248</v>
+      </c>
+      <c r="C52" s="100">
+        <f>D52+E52</f>
+        <v>591000</v>
+      </c>
+      <c r="D52" s="95">
+        <f>C51-E52</f>
+        <v>451888.05599999998</v>
+      </c>
+      <c r="E52" s="95">
+        <f>$H$31*-1</f>
+        <v>139111.94400000002</v>
+      </c>
+      <c r="G52" s="337"/>
+      <c r="H52" s="95"/>
+      <c r="J52" s="95"/>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" t="s">
+        <v>296</v>
+      </c>
+      <c r="C53" s="100">
+        <f>C51-C52</f>
+        <v>0</v>
+      </c>
+      <c r="D53" s="95">
+        <f>D51-D52</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="95">
+        <f>E51-E52</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="95"/>
+      <c r="H53" s="95"/>
+      <c r="J53" s="95"/>
+    </row>
+    <row r="54" spans="2:10" ht="13.5" thickBot="1">
+      <c r="C54" s="112"/>
+      <c r="D54" s="112"/>
+      <c r="E54" s="112"/>
+      <c r="J54" s="95"/>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="J55" s="95"/>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="C56" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E56" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="G51" s="337"/>
-      <c r="H51" s="95"/>
-      <c r="J51" s="95"/>
-    </row>
-    <row r="52" spans="2:10">
-      <c r="C52" s="95"/>
-      <c r="D52" s="113"/>
-      <c r="E52" s="95"/>
-      <c r="G52" s="345" t="s">
+      <c r="G56" s="337"/>
+      <c r="H56" s="95"/>
+      <c r="J56" s="95"/>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="C57" s="95"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="95"/>
+      <c r="G57" s="345" t="s">
         <v>516</v>
       </c>
-      <c r="H52" s="346"/>
-      <c r="J52" s="95"/>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" s="95" t="s">
+      <c r="H57" s="346"/>
+      <c r="J57" s="95"/>
+    </row>
+    <row r="58" spans="2:10">
+      <c r="B58" s="95" t="s">
         <v>246</v>
       </c>
-      <c r="C53" s="95">
-        <f>D47</f>
+      <c r="C58" s="95">
+        <f>D52</f>
         <v>451888.05599999998</v>
       </c>
-      <c r="D53" s="46">
+      <c r="D58" s="46">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E53" s="95">
-        <f>C53*D53</f>
+      <c r="E58" s="95">
+        <f>C58*D58</f>
         <v>11297.2014</v>
       </c>
-      <c r="G53" s="337"/>
-      <c r="H53" s="95"/>
-    </row>
-    <row r="54" spans="2:10">
-      <c r="E54" s="95"/>
-      <c r="G54" s="95"/>
-      <c r="H54" s="95"/>
-    </row>
-    <row r="56" spans="2:10">
-      <c r="D56">
+      <c r="G58" s="337"/>
+      <c r="H58" s="95"/>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="E59" s="95"/>
+      <c r="G59" s="95"/>
+      <c r="H59" s="95"/>
+    </row>
+    <row r="61" spans="2:10">
+      <c r="D61">
         <v>12</v>
       </c>
-      <c r="E56" s="348">
-        <f>D24</f>
+      <c r="E61" s="348">
+        <f>D29</f>
         <v>0.76461599999999996</v>
       </c>
-      <c r="G56" s="349">
-        <f>1-E56</f>
+      <c r="G61" s="349">
+        <f>1-E61</f>
         <v>0.23538400000000004</v>
       </c>
     </row>
-    <row r="57" spans="2:10">
-      <c r="C57">
+    <row r="62" spans="2:10">
+      <c r="C62">
         <v>219</v>
       </c>
-      <c r="D57" s="337">
-        <f>C57/D56</f>
+      <c r="D62" s="337">
+        <f>C62/D61</f>
         <v>18.25</v>
       </c>
-      <c r="E57" s="351">
-        <f>D57*E56</f>
+      <c r="E62" s="351">
+        <f>D62*E61</f>
         <v>13.954241999999999</v>
       </c>
-      <c r="G57" s="351">
-        <f>D57*G56</f>
+      <c r="G62" s="351">
+        <f>D62*G61</f>
         <v>4.2957580000000011</v>
       </c>
     </row>
-    <row r="58" spans="2:10">
-      <c r="C58">
+    <row r="63" spans="2:10">
+      <c r="C63">
         <v>290</v>
       </c>
-      <c r="D58" s="337">
-        <f>C58/D56</f>
+      <c r="D63" s="337">
+        <f>C63/D61</f>
         <v>24.166666666666668</v>
       </c>
-      <c r="E58" s="351">
-        <f>D58*E56</f>
+      <c r="E63" s="351">
+        <f>D63*E61</f>
         <v>18.47822</v>
       </c>
-      <c r="G58" s="351">
-        <f>D58*G56</f>
+      <c r="G63" s="351">
+        <f>D63*G61</f>
         <v>5.6884466666666675</v>
       </c>
     </row>
-    <row r="59" spans="2:10">
-      <c r="D59" s="350">
-        <f>SUM(D57:D58)</f>
+    <row r="64" spans="2:10">
+      <c r="D64" s="350">
+        <f>SUM(D62:D63)</f>
         <v>42.416666666666671</v>
       </c>
-      <c r="E59" s="352">
-        <f>SUM(E57:E58)</f>
+      <c r="E64" s="352">
+        <f>SUM(E62:E63)</f>
         <v>32.432462000000001</v>
       </c>
-      <c r="G59" s="353">
-        <f>SUM(G57:G58)</f>
+      <c r="G64" s="353">
+        <f>SUM(G62:G63)</f>
         <v>9.9842046666666686</v>
       </c>
     </row>
-    <row r="60" spans="2:10">
-      <c r="G60" s="337"/>
-    </row>
-    <row r="61" spans="2:10">
-      <c r="B61" s="139">
+    <row r="65" spans="2:8">
+      <c r="G65" s="337"/>
+    </row>
+    <row r="66" spans="2:8">
+      <c r="B66" s="139">
         <v>45627</v>
       </c>
-      <c r="E61">
+      <c r="E66">
         <v>13.95</v>
       </c>
-      <c r="F61" s="338">
-        <f>E61</f>
+      <c r="F66" s="338">
+        <f>E66</f>
         <v>13.95</v>
       </c>
-      <c r="G61" s="337">
+      <c r="G66" s="337">
         <v>4.3</v>
       </c>
-      <c r="H61" s="338">
-        <f>G61</f>
+      <c r="H66" s="338">
+        <f>G66</f>
         <v>4.3</v>
       </c>
     </row>
-    <row r="62" spans="2:10">
-      <c r="B62" s="139">
+    <row r="67" spans="2:8">
+      <c r="B67" s="139">
         <v>45658</v>
       </c>
-      <c r="E62">
+      <c r="E67">
         <v>32.43</v>
       </c>
-      <c r="F62" s="338">
-        <f>F61+E62</f>
+      <c r="F67" s="338">
+        <f>F66+E67</f>
         <v>46.379999999999995</v>
       </c>
-      <c r="G62" s="337">
-        <f>G59</f>
+      <c r="G67" s="337">
+        <f>G64</f>
         <v>9.9842046666666686</v>
       </c>
-      <c r="H62" s="338">
-        <f>H61+G62</f>
+      <c r="H67" s="338">
+        <f>H66+G67</f>
         <v>14.284204666666668</v>
       </c>
     </row>
-    <row r="63" spans="2:10">
-      <c r="B63" s="139">
+    <row r="68" spans="2:8">
+      <c r="B68" s="139">
         <v>45689</v>
       </c>
-      <c r="E63">
+      <c r="E68">
         <v>32.43</v>
       </c>
-      <c r="F63" s="338">
-        <f t="shared" ref="F63:H65" si="6">F62+E63</f>
+      <c r="F68" s="338">
+        <f t="shared" ref="F68:H70" si="6">F67+E68</f>
         <v>78.81</v>
       </c>
-      <c r="G63" s="337">
-        <f>G62</f>
+      <c r="G68" s="337">
+        <f>G67</f>
         <v>9.9842046666666686</v>
       </c>
-      <c r="H63" s="338">
+      <c r="H68" s="338">
         <f t="shared" si="6"/>
         <v>24.268409333333338</v>
       </c>
     </row>
-    <row r="64" spans="2:10">
-      <c r="B64" s="139">
+    <row r="69" spans="2:8">
+      <c r="B69" s="139">
         <v>45717</v>
       </c>
-      <c r="E64">
+      <c r="E69">
         <v>32.43</v>
       </c>
-      <c r="F64" s="338">
+      <c r="F69" s="338">
         <f t="shared" si="6"/>
         <v>111.24000000000001</v>
       </c>
-      <c r="G64" s="337">
-        <f>G63</f>
+      <c r="G69" s="337">
+        <f>G68</f>
         <v>9.9842046666666686</v>
       </c>
-      <c r="H64" s="338">
+      <c r="H69" s="338">
         <f t="shared" si="6"/>
         <v>34.252614000000008</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
-      <c r="B65" s="139">
+    <row r="70" spans="2:8">
+      <c r="B70" s="139">
         <v>45748</v>
       </c>
-      <c r="E65">
+      <c r="E70">
         <v>32.43</v>
       </c>
-      <c r="F65" s="338">
+      <c r="F70" s="338">
         <f t="shared" si="6"/>
         <v>143.67000000000002</v>
       </c>
-      <c r="G65" s="337">
-        <f>G64</f>
+      <c r="G70" s="337">
+        <f>G69</f>
         <v>9.9842046666666686</v>
       </c>
-      <c r="H65" s="338">
+      <c r="H70" s="338">
         <f t="shared" si="6"/>
         <v>44.236818666666679</v>
       </c>
     </row>
-    <row r="66" spans="2:8">
-      <c r="B66" s="139">
-        <v>45778</v>
-      </c>
-      <c r="F66" s="338"/>
-      <c r="H66" s="1"/>
-    </row>
-    <row r="67" spans="2:8">
-      <c r="B67" s="139">
-        <v>45809</v>
-      </c>
-      <c r="F67" s="338"/>
-      <c r="H67" s="1"/>
-    </row>
-    <row r="68" spans="2:8">
-      <c r="B68" s="139">
-        <v>45839</v>
-      </c>
-      <c r="F68" s="338"/>
-      <c r="H68" s="1"/>
-    </row>
-    <row r="69" spans="2:8">
-      <c r="B69" s="139">
-        <v>45870</v>
-      </c>
-      <c r="F69" s="338"/>
-      <c r="H69" s="1"/>
-    </row>
-    <row r="70" spans="2:8">
-      <c r="B70" s="139">
-        <v>45901</v>
-      </c>
-      <c r="F70" s="338"/>
-      <c r="H70" s="1"/>
-    </row>
     <row r="71" spans="2:8">
       <c r="B71" s="139">
-        <v>45931</v>
+        <v>45778</v>
       </c>
       <c r="F71" s="338"/>
       <c r="H71" s="1"/>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" s="139">
-        <v>45962</v>
+        <v>45809</v>
       </c>
       <c r="F72" s="338"/>
       <c r="H72" s="1"/>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" s="139">
-        <v>45992</v>
+        <v>45839</v>
       </c>
       <c r="F73" s="338"/>
       <c r="H73" s="1"/>
     </row>
     <row r="74" spans="2:8">
-      <c r="B74" s="139"/>
+      <c r="B74" s="139">
+        <v>45870</v>
+      </c>
+      <c r="F74" s="338"/>
+      <c r="H74" s="1"/>
     </row>
     <row r="75" spans="2:8">
-      <c r="B75" s="139"/>
+      <c r="B75" s="139">
+        <v>45901</v>
+      </c>
+      <c r="F75" s="338"/>
+      <c r="H75" s="1"/>
     </row>
     <row r="76" spans="2:8">
-      <c r="B76" s="139"/>
+      <c r="B76" s="139">
+        <v>45931</v>
+      </c>
+      <c r="F76" s="338"/>
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" spans="2:8">
+      <c r="B77" s="139">
+        <v>45962</v>
+      </c>
+      <c r="F77" s="338"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="2:8">
+      <c r="B78" s="139">
+        <v>45992</v>
+      </c>
+      <c r="F78" s="338"/>
+      <c r="H78" s="1"/>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="B79" s="139"/>
+    </row>
+    <row r="80" spans="2:8">
+      <c r="B80" s="139"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="139"/>
     </row>
   </sheetData>
   <phoneticPr fontId="49" type="noConversion"/>
@@ -11934,7 +11985,7 @@
         <v>44413</v>
       </c>
       <c r="B67" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C67"/>
       <c r="E67" s="2" t="s">
@@ -12706,7 +12757,7 @@
     <row r="20" spans="1:11">
       <c r="A20" s="194"/>
       <c r="B20" s="218" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C20" s="196"/>
       <c r="D20" s="197"/>

--- a/26-tdy/02-26-sny.xlsx
+++ b/26-tdy/02-26-sny.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\26-tdy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343588F4-9310-4FE6-A551-F5F77414C552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2484EAD6-320E-415E-9E6D-B545DFFFED15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="773" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="773" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TPLM" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="529">
   <si>
     <t>Ödeme Teminat Tablosu</t>
   </si>
@@ -1684,6 +1684,21 @@
   </si>
   <si>
     <t>sny CD Ali demirel</t>
+  </si>
+  <si>
+    <t>30-09-2024 – 29-09-2025 kira bedeli</t>
+  </si>
+  <si>
+    <t>12 ay</t>
+  </si>
+  <si>
+    <t>oturulan ay</t>
+  </si>
+  <si>
+    <t>eylül 2024 tüfe</t>
+  </si>
+  <si>
+    <t>2023 kirası</t>
   </si>
 </sst>
 </file>
@@ -5306,12 +5321,12 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="2" max="2" width="36.140625" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="12.140625" customWidth="1"/>
     <col min="8" max="8" width="9.140625" customWidth="1"/>
@@ -5386,7 +5401,7 @@
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="18">
-        <f>G40</f>
+        <f>G85</f>
         <v>0</v>
       </c>
       <c r="F5" s="3"/>
@@ -5398,7 +5413,7 @@
       </c>
       <c r="C6" s="14"/>
       <c r="E6" s="19">
-        <f>G37</f>
+        <f>G82</f>
         <v>-1200</v>
       </c>
       <c r="F6" s="14"/>
@@ -5456,7 +5471,7 @@
       <c r="E10" s="24"/>
       <c r="F10" s="25"/>
       <c r="G10" s="3">
-        <f t="shared" ref="G10:G20" si="0">E10-F10+G9</f>
+        <f t="shared" ref="G10:G28" si="0">E10-F10+G9</f>
         <v>0</v>
       </c>
     </row>
@@ -5543,11 +5558,11 @@
       </c>
       <c r="F16" s="28"/>
       <c r="G16" s="3">
-        <f t="shared" si="0"/>
+        <f>E16-F16+G15</f>
         <v>110513</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:7">
       <c r="A17" s="26"/>
       <c r="E17" s="27"/>
       <c r="F17" s="28"/>
@@ -5556,7 +5571,7 @@
         <v>110513</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15">
+    <row r="18" spans="1:7" ht="15">
       <c r="A18" s="26"/>
       <c r="B18" s="293">
         <v>45739</v>
@@ -5568,7 +5583,7 @@
         <v>110513</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:7">
       <c r="A19" s="26"/>
       <c r="E19" s="27"/>
       <c r="F19" s="28"/>
@@ -5577,7 +5592,7 @@
         <v>110513</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:7">
       <c r="A20" s="26"/>
       <c r="E20" s="27"/>
       <c r="F20" s="28"/>
@@ -5586,566 +5601,778 @@
         <v>110513</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:7">
       <c r="A21" s="26"/>
       <c r="E21" s="30"/>
       <c r="F21" s="31"/>
       <c r="G21" s="31"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:7">
       <c r="A22" s="26"/>
-      <c r="E22" s="30"/>
+      <c r="B22" t="s">
+        <v>528</v>
+      </c>
+      <c r="E22" s="30">
+        <v>96000</v>
+      </c>
       <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="26"/>
+      <c r="B23" t="s">
+        <v>527</v>
+      </c>
+      <c r="C23" s="337">
+        <v>63.47</v>
+      </c>
+      <c r="E23" s="30">
+        <f>E22*C23/100</f>
+        <v>60931.199999999997</v>
+      </c>
+      <c r="F23" s="31"/>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="26"/>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="30"/>
+      <c r="B24" s="42" t="s">
+        <v>524</v>
+      </c>
+      <c r="E24" s="30">
+        <f>SUM(E22:E23)</f>
+        <v>156931.20000000001</v>
+      </c>
       <c r="F24" s="31"/>
-      <c r="G24" s="31">
-        <v>-1200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="26"/>
       <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25">
-        <v>40</v>
-      </c>
-      <c r="E25" s="31">
-        <v>483.72</v>
-      </c>
-      <c r="F25" s="31">
-        <v>483.72</v>
-      </c>
-      <c r="G25" s="31">
-        <f t="shared" ref="G25:G36" si="1">E25-F25+G24</f>
-        <v>-1200</v>
-      </c>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8">
+        <v>525</v>
+      </c>
+      <c r="C25">
+        <v>12</v>
+      </c>
+      <c r="E25" s="30">
+        <f>E24/C25</f>
+        <v>13077.6</v>
+      </c>
+      <c r="F25" s="31"/>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="26"/>
       <c r="B26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="31">
-        <v>439.85</v>
-      </c>
-      <c r="F26" s="31">
-        <v>439.85</v>
-      </c>
-      <c r="G26" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8">
+        <v>526</v>
+      </c>
+      <c r="C26">
+        <v>3.5</v>
+      </c>
+      <c r="E26" s="30">
+        <f>E25*C26</f>
+        <v>45771.6</v>
+      </c>
+      <c r="F26" s="31"/>
+      <c r="G26" s="3">
+        <f t="shared" si="0"/>
+        <v>45771.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="26"/>
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="31"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="G27" s="3">
+        <f t="shared" si="0"/>
+        <v>45771.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15">
       <c r="A28" s="26"/>
-      <c r="B28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="31"/>
+      <c r="B28" s="293">
+        <v>46079</v>
+      </c>
+      <c r="E28" s="30"/>
       <c r="F28" s="31"/>
-      <c r="G28" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="G28" s="3">
+        <f t="shared" si="0"/>
+        <v>45771.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="26"/>
-      <c r="B29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="31"/>
+      <c r="E29" s="30"/>
       <c r="F29" s="31"/>
-      <c r="G29" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="G29" s="31"/>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="26"/>
-      <c r="B30" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="31"/>
+      <c r="E30" s="30"/>
       <c r="F30" s="31"/>
-      <c r="G30" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="G30" s="31"/>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="26"/>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="31"/>
+      <c r="E31" s="30"/>
       <c r="F31" s="31"/>
-      <c r="G31" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="G31" s="31"/>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="26"/>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="31"/>
+      <c r="E32" s="30"/>
       <c r="F32" s="31"/>
-      <c r="G32" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H32" s="3"/>
+      <c r="G32" s="31"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="26"/>
-      <c r="B33" t="s">
-        <v>90</v>
-      </c>
       <c r="E33" s="30"/>
       <c r="F33" s="31"/>
-      <c r="G33" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H33" s="3"/>
+      <c r="G33" s="31"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="26"/>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
       <c r="E34" s="30"/>
       <c r="F34" s="31"/>
-      <c r="G34" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H34" s="3"/>
+      <c r="G34" s="31"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="26"/>
-      <c r="B35" t="s">
-        <v>40</v>
-      </c>
       <c r="E35" s="30"/>
       <c r="F35" s="31"/>
-      <c r="G35" s="31">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
-      <c r="H35" s="3"/>
+      <c r="G35" s="31"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="32"/>
-      <c r="B36" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34">
-        <f t="shared" si="1"/>
-        <v>-1200</v>
-      </c>
+      <c r="A36" s="26"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="35">
-        <v>45291</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36">
-        <f>SUM(D25:D36)</f>
-        <v>40</v>
-      </c>
-      <c r="E37" s="37"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="39">
-        <f>E37-F37+G36</f>
-        <v>-1200</v>
-      </c>
+      <c r="A37" s="26"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="26"/>
       <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="7"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="A39" s="26"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="88" t="s">
-        <v>250</v>
-      </c>
-      <c r="B40" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="43">
-        <f>SUM(F41:F55)</f>
-        <v>0</v>
-      </c>
+      <c r="A40" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="34"/>
+      <c r="G40" s="31"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="7"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="A41" s="26"/>
+      <c r="B41" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="30"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="7"/>
+      <c r="A42" s="26"/>
       <c r="B42" t="s">
-        <v>218</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="D42">
+        <v>40</v>
+      </c>
+      <c r="E42" s="31">
+        <v>483.72</v>
+      </c>
+      <c r="F42" s="31">
+        <v>483.72</v>
+      </c>
+      <c r="G42" s="31"/>
+      <c r="H42" s="3"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="7"/>
+      <c r="A43" s="26"/>
       <c r="B43" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="E43" s="31">
+        <v>439.85</v>
+      </c>
+      <c r="F43" s="31">
+        <v>439.85</v>
+      </c>
+      <c r="G43" s="31"/>
+      <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="7"/>
-      <c r="B44" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42">
-        <v>96000</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="44"/>
+      <c r="A44" s="26"/>
+      <c r="B44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="3"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="84">
-        <v>45237</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+      <c r="A45" s="26"/>
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="3"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="B46" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C46" s="1"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
+      <c r="A46" s="26"/>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="B47" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C47" s="1"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
+      <c r="A47" s="26"/>
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="B48" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="B49" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="B50" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="B51" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="B52" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="B56" t="s">
-        <v>228</v>
-      </c>
-      <c r="D56" s="3"/>
+      <c r="A48" s="26"/>
+      <c r="B48" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="26"/>
+      <c r="B49" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="26"/>
+      <c r="B50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="30"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="26"/>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51" s="30"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="26"/>
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" s="30"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="32"/>
+      <c r="B53" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="31"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="35">
+        <v>45291</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36">
+        <f>SUM(D42:D53)</f>
+        <v>40</v>
+      </c>
+      <c r="E54" s="37"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="31"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="26"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="31"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="7"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="B57" t="s">
+      <c r="G56" s="31"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="88" t="s">
+        <v>250</v>
+      </c>
+      <c r="B57" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="31"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="7"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="G58" s="31"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="7"/>
+      <c r="B59" t="s">
+        <v>218</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="31"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="7"/>
+      <c r="B60" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="31"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="7"/>
+      <c r="B61" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" s="42"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42">
+        <v>96000</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="31"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="84">
+        <v>45237</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="31"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="B63" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="31"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="B64" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="31"/>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="B65" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="31"/>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="B66" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="31"/>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="B67" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="31"/>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="B68" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="34" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="B69" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="31">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="G70" s="31">
+        <f>E42-F42+G69</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="G71" s="31">
+        <f>E43-F43+G70</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="G72" s="31">
+        <f>E44-F44+G71</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="B73" t="s">
+        <v>228</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="31">
+        <f>E45-F45+G72</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="B74" t="s">
         <v>229</v>
       </c>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3">
-        <f t="shared" ref="F57:F71" si="2">F56+D57-E57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="54"/>
-      <c r="D58" s="3"/>
-      <c r="F58" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="54">
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3">
+        <f t="shared" ref="F74:F88" si="1">F73+D74-E74</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="31">
+        <f>E46-F46+G73</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="54"/>
+      <c r="D75" s="3"/>
+      <c r="F75" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G75" s="31">
+        <f>E47-F47+G74</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="54">
         <v>44956</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B76" t="s">
         <v>230</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D76" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
-        <f t="shared" si="2"/>
+      <c r="F76" s="3">
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="54">
+      <c r="G76" s="31">
+        <f>E48-F48+G75</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="54">
         <v>44985</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B77" t="s">
         <v>231</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D77" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
-        <f t="shared" si="2"/>
+      <c r="F77" s="3">
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="54">
+      <c r="G77" s="31">
+        <f>E49-F49+G76</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="54">
         <v>45015</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B78" t="s">
         <v>232</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D78" s="3">
         <v>1000</v>
       </c>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3">
-        <f t="shared" si="2"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3">
+        <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="54">
+      <c r="G78" s="31">
+        <f>E50-F50+G77</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="54">
         <v>45046</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B79" t="s">
         <v>233</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D79" s="3">
         <v>1000</v>
       </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3">
-        <f t="shared" si="2"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3">
+        <f t="shared" si="1"/>
         <v>4000</v>
       </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="54"/>
-      <c r="F63" s="3">
-        <f t="shared" si="2"/>
+      <c r="G79" s="31">
+        <f>E51-F51+G78</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="54"/>
+      <c r="F80" s="3">
+        <f t="shared" si="1"/>
         <v>4000</v>
       </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="54"/>
-      <c r="B64" s="1" t="s">
+      <c r="G80" s="31">
+        <f>E52-F52+G79</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="54"/>
+      <c r="B81" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C64" s="1"/>
-      <c r="D64" s="3">
+      <c r="C81" s="1"/>
+      <c r="D81" s="3">
         <v>400</v>
       </c>
-      <c r="F64" s="3">
-        <f t="shared" si="2"/>
+      <c r="F81" s="3">
+        <f t="shared" si="1"/>
         <v>4400</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="54"/>
-      <c r="B65" t="s">
+      <c r="G81" s="34">
+        <f>E53-F53+G80</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="54"/>
+      <c r="B82" t="s">
         <v>235</v>
       </c>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3">
-        <f t="shared" si="2"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3">
+        <f t="shared" si="1"/>
         <v>4400</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="54"/>
-      <c r="B66" t="s">
+      <c r="G82" s="39">
+        <f>E54-F54+G81</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="54"/>
+      <c r="B83" t="s">
         <v>236</v>
       </c>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3">
-        <f t="shared" si="2"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3">
+        <f t="shared" si="1"/>
         <v>4400</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="54"/>
-      <c r="D67" s="3"/>
-      <c r="F67" s="3">
-        <f t="shared" si="2"/>
+      <c r="G83" s="30"/>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="54"/>
+      <c r="D84" s="3"/>
+      <c r="F84" s="3">
+        <f t="shared" si="1"/>
         <v>4400</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="54">
+      <c r="G84" s="3"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="54">
         <v>44998</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B85" t="s">
         <v>237</v>
       </c>
-      <c r="D68" s="3"/>
-      <c r="E68">
+      <c r="D85" s="3"/>
+      <c r="E85">
         <v>2400</v>
       </c>
-      <c r="F68" s="3">
-        <f t="shared" si="2"/>
+      <c r="F85" s="3">
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="54">
+      <c r="G85" s="43">
+        <f>SUM(F58:F72)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="54">
         <v>44998</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B86" t="s">
         <v>237</v>
       </c>
-      <c r="E69">
+      <c r="E86">
         <v>2400</v>
       </c>
-      <c r="F69" s="3">
-        <f t="shared" si="2"/>
+      <c r="F86" s="3">
+        <f t="shared" si="1"/>
         <v>-400</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="1" t="s">
+    <row r="87" spans="1:7">
+      <c r="B87" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C70" s="1"/>
-      <c r="E70">
+      <c r="C87" s="1"/>
+      <c r="E87">
         <v>-342.4</v>
       </c>
-      <c r="F70" s="3">
-        <f t="shared" si="2"/>
+      <c r="F87" s="3">
+        <f t="shared" si="1"/>
         <v>-57.600000000000023</v>
       </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="1" t="s">
+      <c r="G87" s="3"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="B88" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="E71">
+      <c r="C88" s="1"/>
+      <c r="E88">
         <v>-57.6</v>
       </c>
-      <c r="F71" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F88" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G88" s="3"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="G89" s="44"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="G90" s="3"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="G91" s="3"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="G92" s="3"/>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="G93" s="3"/>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="G94" s="3"/>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="G95" s="3"/>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="G96" s="3"/>
+    </row>
+    <row r="97" spans="7:7">
+      <c r="G97" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.39370078740157505" right="0.23622047244094502" top="0.70905511811023614" bottom="0.7062992125984251" header="0.31535433070866109" footer="0.3125984251968501"/>

--- a/26-tdy/02-26-sny.xlsx
+++ b/26-tdy/02-26-sny.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\26-tdy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2484EAD6-320E-415E-9E6D-B545DFFFED15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA1D414-F836-4FB8-97EF-A77F8741C7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="773" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" tabRatio="773" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TPLM" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="532">
   <si>
     <t>Ödeme Teminat Tablosu</t>
   </si>
@@ -1699,6 +1699,15 @@
   </si>
   <si>
     <t>2023 kirası</t>
+  </si>
+  <si>
+    <t>2025 kirası</t>
+  </si>
+  <si>
+    <t>2026 kirası</t>
+  </si>
+  <si>
+    <t>2027 kirası</t>
   </si>
 </sst>
 </file>
@@ -6084,19 +6093,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="G70" s="31">
-        <f>E42-F42+G69</f>
+        <f t="shared" ref="G70:G82" si="1">E42-F42+G69</f>
         <v>-1200</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="G71" s="31">
-        <f>E43-F43+G70</f>
+        <f t="shared" si="1"/>
         <v>-1200</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="G72" s="31">
-        <f>E44-F44+G71</f>
+        <f t="shared" si="1"/>
         <v>-1200</v>
       </c>
     </row>
@@ -6108,7 +6117,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="31">
-        <f>E45-F45+G72</f>
+        <f t="shared" si="1"/>
         <v>-1200</v>
       </c>
     </row>
@@ -6119,11 +6128,11 @@
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3">
-        <f t="shared" ref="F74:F88" si="1">F73+D74-E74</f>
+        <f t="shared" ref="F74:F88" si="2">F73+D74-E74</f>
         <v>0</v>
       </c>
       <c r="G74" s="31">
-        <f>E46-F46+G73</f>
+        <f t="shared" si="1"/>
         <v>-1200</v>
       </c>
     </row>
@@ -6131,11 +6140,11 @@
       <c r="A75" s="54"/>
       <c r="D75" s="3"/>
       <c r="F75" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G75" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G75" s="31">
-        <f>E47-F47+G74</f>
         <v>-1200</v>
       </c>
     </row>
@@ -6150,11 +6159,11 @@
         <v>1000</v>
       </c>
       <c r="F76" s="3">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="G76" s="31">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="G76" s="31">
-        <f>E48-F48+G75</f>
         <v>-1200</v>
       </c>
     </row>
@@ -6169,11 +6178,11 @@
         <v>1000</v>
       </c>
       <c r="F77" s="3">
+        <f t="shared" si="2"/>
+        <v>2000</v>
+      </c>
+      <c r="G77" s="31">
         <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-      <c r="G77" s="31">
-        <f>E49-F49+G76</f>
         <v>-1200</v>
       </c>
     </row>
@@ -6189,11 +6198,11 @@
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="G78" s="31">
         <f t="shared" si="1"/>
-        <v>3000</v>
-      </c>
-      <c r="G78" s="31">
-        <f>E50-F50+G77</f>
         <v>-1200</v>
       </c>
     </row>
@@ -6209,22 +6218,22 @@
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3">
+        <f t="shared" si="2"/>
+        <v>4000</v>
+      </c>
+      <c r="G79" s="31">
         <f t="shared" si="1"/>
-        <v>4000</v>
-      </c>
-      <c r="G79" s="31">
-        <f>E51-F51+G78</f>
         <v>-1200</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="54"/>
       <c r="F80" s="3">
+        <f t="shared" si="2"/>
+        <v>4000</v>
+      </c>
+      <c r="G80" s="31">
         <f t="shared" si="1"/>
-        <v>4000</v>
-      </c>
-      <c r="G80" s="31">
-        <f>E52-F52+G79</f>
         <v>-1200</v>
       </c>
     </row>
@@ -6238,11 +6247,11 @@
         <v>400</v>
       </c>
       <c r="F81" s="3">
+        <f t="shared" si="2"/>
+        <v>4400</v>
+      </c>
+      <c r="G81" s="34">
         <f t="shared" si="1"/>
-        <v>4400</v>
-      </c>
-      <c r="G81" s="34">
-        <f>E53-F53+G80</f>
         <v>-1200</v>
       </c>
     </row>
@@ -6254,11 +6263,11 @@
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3">
+        <f t="shared" si="2"/>
+        <v>4400</v>
+      </c>
+      <c r="G82" s="39">
         <f t="shared" si="1"/>
-        <v>4400</v>
-      </c>
-      <c r="G82" s="39">
-        <f>E54-F54+G81</f>
         <v>-1200</v>
       </c>
     </row>
@@ -6270,7 +6279,7 @@
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4400</v>
       </c>
       <c r="G83" s="30"/>
@@ -6279,7 +6288,7 @@
       <c r="A84" s="54"/>
       <c r="D84" s="3"/>
       <c r="F84" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4400</v>
       </c>
       <c r="G84" s="3"/>
@@ -6296,7 +6305,7 @@
         <v>2400</v>
       </c>
       <c r="F85" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
       <c r="G85" s="43">
@@ -6315,7 +6324,7 @@
         <v>2400</v>
       </c>
       <c r="F86" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-400</v>
       </c>
     </row>
@@ -6328,7 +6337,7 @@
         <v>-342.4</v>
       </c>
       <c r="F87" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-57.600000000000023</v>
       </c>
       <c r="G87" s="3"/>
@@ -6342,7 +6351,7 @@
         <v>-57.6</v>
       </c>
       <c r="F88" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G88" s="3"/>
@@ -9071,7 +9080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="7" customWidth="1"/>
@@ -9563,10 +9572,27 @@
       <c r="E41"/>
     </row>
     <row r="42" spans="1:8">
+      <c r="C42">
+        <f>D47</f>
+        <v>220449.6</v>
+      </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
     <row r="43" spans="1:8">
+      <c r="A43" s="7">
+        <v>46295</v>
+      </c>
+      <c r="B43" t="s">
+        <v>531</v>
+      </c>
+      <c r="C43">
+        <v>32</v>
+      </c>
+      <c r="D43">
+        <f>C42*1.62</f>
+        <v>357128.35200000001</v>
+      </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
@@ -9579,92 +9605,72 @@
       <c r="H45" s="3"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="26">
-        <v>45166</v>
-      </c>
-      <c r="B46" t="s">
-        <v>42</v>
-      </c>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
+      <c r="C46">
+        <f>D51</f>
+        <v>136080</v>
+      </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="26"/>
+      <c r="A47" s="7">
+        <v>45930</v>
+      </c>
       <c r="B47" t="s">
-        <v>43</v>
-      </c>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
+        <v>530</v>
+      </c>
+      <c r="C47">
+        <v>37</v>
+      </c>
+      <c r="D47">
+        <f>C46*1.62</f>
+        <v>220449.6</v>
+      </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="26"/>
-      <c r="B48" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="26">
-        <v>45170</v>
-      </c>
-      <c r="B49" t="s">
-        <v>45</v>
-      </c>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="26">
-        <v>45174</v>
-      </c>
-      <c r="B50" t="s">
-        <v>46</v>
-      </c>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
+      <c r="C50">
+        <v>84000</v>
+      </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="26"/>
+      <c r="A51" s="7">
+        <v>45565</v>
+      </c>
       <c r="B51" t="s">
-        <v>47</v>
-      </c>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
+        <v>529</v>
+      </c>
+      <c r="C51">
+        <v>62</v>
+      </c>
+      <c r="D51">
+        <f>C50*1.62</f>
+        <v>136080</v>
+      </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="26"/>
-      <c r="B52" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="26"/>
+      <c r="A53" s="26">
+        <v>45166</v>
+      </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D53" s="30"/>
       <c r="E53" s="30"/>
@@ -9675,7 +9681,7 @@
     <row r="54" spans="1:8">
       <c r="A54" s="26"/>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D54" s="30"/>
       <c r="E54" s="30"/>
@@ -9686,7 +9692,7 @@
     <row r="55" spans="1:8">
       <c r="A55" s="26"/>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D55" s="30"/>
       <c r="E55" s="30"/>
@@ -9695,9 +9701,11 @@
       <c r="H55" s="3"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="26"/>
+      <c r="A56" s="26">
+        <v>45170</v>
+      </c>
       <c r="B56" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D56" s="30"/>
       <c r="E56" s="30"/>
@@ -9707,10 +9715,10 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="26">
-        <v>45196</v>
+        <v>45174</v>
       </c>
       <c r="B57" t="s">
-        <v>257</v>
+        <v>46</v>
       </c>
       <c r="D57" s="30"/>
       <c r="E57" s="30"/>
@@ -9721,7 +9729,7 @@
     <row r="58" spans="1:8">
       <c r="A58" s="26"/>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D58" s="30"/>
       <c r="E58" s="30"/>
@@ -9730,230 +9738,244 @@
       <c r="H58" s="3"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="7">
+      <c r="A59" s="26"/>
+      <c r="B59" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="26"/>
+      <c r="B60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="26"/>
+      <c r="B61" t="s">
+        <v>50</v>
+      </c>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="26"/>
+      <c r="B62" t="s">
+        <v>51</v>
+      </c>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="26"/>
+      <c r="B63" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="26">
         <v>45196</v>
       </c>
-      <c r="B59" t="s">
-        <v>256</v>
-      </c>
-      <c r="D59" s="3"/>
-      <c r="F59" s="3"/>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="D60" s="3"/>
-      <c r="F60" s="3"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="F61" s="44"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="8"/>
-      <c r="F62" s="45"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="8"/>
-      <c r="F63" s="45"/>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="45"/>
+      <c r="B64" t="s">
+        <v>257</v>
+      </c>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="E65" s="45"/>
-      <c r="F65" s="3"/>
+      <c r="A65" s="26"/>
+      <c r="B65" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="B66" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="45" t="s">
-        <v>55</v>
-      </c>
+      <c r="A66" s="7">
+        <v>45196</v>
+      </c>
+      <c r="B66" t="s">
+        <v>256</v>
+      </c>
+      <c r="D66" s="3"/>
       <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
       <c r="D67" s="3"/>
       <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="B68" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" s="47"/>
-      <c r="D68" s="21"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="F68" s="44"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="B69" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="C69" s="48"/>
-      <c r="D69" s="15">
-        <f>SUM(D79:D81)</f>
-        <v>42000</v>
-      </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="8"/>
+      <c r="F69" s="45"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="B70" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="C70" s="48"/>
-      <c r="D70" s="16">
-        <f>SUM(E79:E81)</f>
-        <v>40000</v>
-      </c>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="8"/>
+      <c r="F70" s="45"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="B71" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="C71" s="48"/>
-      <c r="D71" s="49">
-        <f>F81</f>
-        <v>2000</v>
-      </c>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="45"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="B72" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C72" s="48"/>
-      <c r="D72" s="45">
-        <f>E103</f>
-        <v>0</v>
-      </c>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="E72" s="45"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="B73" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="48"/>
-      <c r="D73" s="45">
-        <v>0</v>
+      <c r="B73" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" s="8"/>
+      <c r="D73" s="45" t="s">
+        <v>55</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="B74" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="C74" s="33"/>
-      <c r="D74" s="50">
-        <f>D70-D72</f>
-        <v>40000</v>
-      </c>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="B75" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C75" s="8"/>
-      <c r="D75" s="3"/>
+      <c r="B75" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="47"/>
+      <c r="D75" s="21"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="B76" t="s">
-        <v>61</v>
-      </c>
-      <c r="D76" s="3"/>
+      <c r="B76" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C76" s="48"/>
+      <c r="D76" s="15">
+        <f>SUM(D86:D88)</f>
+        <v>42000</v>
+      </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="D77" s="3"/>
+      <c r="B77" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C77" s="48"/>
+      <c r="D77" s="16">
+        <f>SUM(E86:E88)</f>
+        <v>40000</v>
+      </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="D78" s="3"/>
+      <c r="B78" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="49">
+        <f>F88</f>
+        <v>2000</v>
+      </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="B79" t="s">
-        <v>62</v>
-      </c>
-      <c r="D79" s="3"/>
+      <c r="B79" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" s="48"/>
+      <c r="D79" s="45">
+        <f>E110</f>
+        <v>0</v>
+      </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="7">
-        <v>44885</v>
-      </c>
-      <c r="B80" t="s">
-        <v>63</v>
-      </c>
-      <c r="D80" s="3">
-        <v>42000</v>
-      </c>
-      <c r="E80" s="3">
-        <v>40000</v>
-      </c>
-      <c r="F80" s="3">
-        <f>F76+D80-E80</f>
-        <v>2000</v>
-      </c>
+      <c r="B80" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="48"/>
+      <c r="D80" s="45">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="D81" s="3"/>
-      <c r="F81" s="3">
-        <f>F80+D81-E81</f>
-        <v>2000</v>
-      </c>
+      <c r="B81" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="33"/>
+      <c r="D81" s="50">
+        <f>D77-D79</f>
+        <v>40000</v>
+      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
     </row>
     <row r="82" spans="1:8">
+      <c r="B82" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C82" s="8"/>
       <c r="D82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -9961,7 +9983,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="B83" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D83" s="3"/>
       <c r="F83" s="3"/>
@@ -9969,145 +9991,128 @@
       <c r="H83" s="3"/>
     </row>
     <row r="84" spans="1:8">
-      <c r="B84" t="s">
-        <v>65</v>
-      </c>
       <c r="D84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="B85" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C85" s="8"/>
       <c r="D85" s="3"/>
-      <c r="F85" s="45"/>
+      <c r="F85" s="3"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="B86" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C86" s="1"/>
+      <c r="B86" t="s">
+        <v>62</v>
+      </c>
       <c r="D86" s="3"/>
-      <c r="F86" s="45"/>
+      <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="B87" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C87" s="8"/>
-      <c r="F87" s="45"/>
+      <c r="A87" s="7">
+        <v>44885</v>
+      </c>
+      <c r="B87" t="s">
+        <v>63</v>
+      </c>
+      <c r="D87" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E87" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F87" s="3">
+        <f>F83+D87-E87</f>
+        <v>2000</v>
+      </c>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="B88" t="s">
-        <v>69</v>
-      </c>
-      <c r="F88" s="45"/>
+      <c r="D88" s="3"/>
+      <c r="F88" s="3">
+        <f>F87+D88-E88</f>
+        <v>2000</v>
+      </c>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="B89" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C89" s="8"/>
-      <c r="E89"/>
-      <c r="F89" s="45"/>
+      <c r="D89" s="3"/>
+      <c r="F89" s="3"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
     </row>
     <row r="90" spans="1:8">
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
+      <c r="B90" t="s">
+        <v>64</v>
+      </c>
       <c r="D90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="7">
-        <v>45132</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C91" s="3"/>
+      <c r="B91" t="s">
+        <v>65</v>
+      </c>
       <c r="D91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="7">
-        <v>45137</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C92" s="3"/>
+      <c r="B92" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C92" s="8"/>
       <c r="D92" s="3"/>
-      <c r="F92" s="3"/>
+      <c r="F92" s="45"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="7">
-        <v>45148</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C93" s="3"/>
+      <c r="B93" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C93" s="1"/>
       <c r="D93" s="3"/>
-      <c r="F93" s="3"/>
+      <c r="F93" s="45"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="7">
-        <v>45160</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="F94" s="3"/>
+      <c r="B94" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C94" s="8"/>
+      <c r="F94" s="45"/>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="B95" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="F95" s="3"/>
+      <c r="B95" t="s">
+        <v>69</v>
+      </c>
+      <c r="F95" s="45"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="B96" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="F96" s="3"/>
+      <c r="B96" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C96" s="8"/>
+      <c r="E96"/>
+      <c r="F96" s="45"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="B97" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="F97" s="3"/>
@@ -10115,8 +10120,11 @@
       <c r="H97" s="3"/>
     </row>
     <row r="98" spans="1:8">
+      <c r="A98" s="7">
+        <v>45132</v>
+      </c>
       <c r="B98" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
@@ -10125,8 +10133,11 @@
       <c r="H98" s="3"/>
     </row>
     <row r="99" spans="1:8">
+      <c r="A99" s="7">
+        <v>45137</v>
+      </c>
       <c r="B99" s="3" t="s">
-        <v>78</v>
+        <v>459</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
@@ -10135,8 +10146,11 @@
       <c r="H99" s="3"/>
     </row>
     <row r="100" spans="1:8">
+      <c r="A100" s="7">
+        <v>45148</v>
+      </c>
       <c r="B100" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -10146,10 +10160,10 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="7">
-        <v>45167</v>
+        <v>45160</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
@@ -10159,7 +10173,7 @@
     </row>
     <row r="102" spans="1:8">
       <c r="B102" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
@@ -10169,7 +10183,7 @@
     </row>
     <row r="103" spans="1:8">
       <c r="B103" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
@@ -10179,9 +10193,82 @@
     </row>
     <row r="104" spans="1:8">
       <c r="B104" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="B105" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="B106" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="B107" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="7">
+        <v>45167</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="B109" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="B110" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="B111" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C104" s="3"/>
+      <c r="C111" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.39370078740157505" right="0.23622047244094502" top="0.70905511811023614" bottom="0.7062992125984251" header="0.31535433070866109" footer="0.3125984251968501"/>
